--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-03T21:32:28.591Z</t>
+    <t>2026-06-09T15:00:41.850Z</t>
   </si>
   <si>
     <t>UnumGroup | Helping the working world thrive throughout life's moments®</t>
